--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_truth(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_truth(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="19305" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_真结局" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="460">
   <si>
     <t>ID</t>
   </si>
@@ -87,6 +87,9 @@
     <t>铁盒内的机械心脏轻微搏动了一下，将你从短暂地失神中拉回到当下。你迅速坐进自己的舱体，戴上头盔，把视线连通不舍的情绪一并收束回了心底柔软的角落。</t>
   </si>
   <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -285,6 +288,9 @@
     <t>老板是一个戴着眼镜，身材方正的中年黑人男性，他平日里一直对你严格要求，从新闻排版到细节校对，严谨得令人生厌。却又在你们真正触及危险的秘密时及时拉你们一把。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=20</t>
   </si>
   <si>
@@ -327,6 +333,9 @@
     <t>两个熟悉的面孔正凑在前台的咖啡机旁等着你的加入，听见你推门进来的动静，齐刷刷转过了头。</t>
   </si>
   <si>
+    <t>11 enhanced the_mountain-hope-background</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=24</t>
   </si>
   <si>
@@ -589,6 +598,9 @@
   </si>
   <si>
     <t>直到一面冷白色的天花板在你模糊的视野中渐渐显形，你这才吸入醒来后的第一缕空气，熟悉的消毒水混杂这甜腻的麻药味争先恐后地涌入鼻腔，和你记忆里圣诺汀精神病院的味道一模一样。</t>
+  </si>
+  <si>
+    <t>16 enhanced_suspence</t>
   </si>
   <si>
     <t>bgfade(sntzm_truth(2)_53,1)</t>
@@ -2726,7 +2738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:12">
+    <row r="2" ht="60" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2752,21 +2764,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="54" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2784,7 +2796,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2799,12 +2811,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="40.5" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2822,7 +2834,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2837,12 +2849,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2860,7 +2872,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2875,12 +2887,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2898,10 +2910,10 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
@@ -2913,12 +2925,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2936,7 +2948,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2951,12 +2963,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2974,7 +2986,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2989,12 +3001,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="42" spans="1:12">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3012,7 +3024,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3027,12 +3039,12 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -3050,7 +3062,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3065,12 +3077,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:12">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3088,7 +3100,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3103,12 +3115,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="42" spans="1:12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3126,7 +3138,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3138,15 +3150,15 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" ht="55.5" spans="1:12">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3164,7 +3176,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3179,12 +3191,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="69" spans="1:12">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3202,7 +3214,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3214,15 +3226,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="27" spans="1:12">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3240,7 +3252,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3255,12 +3267,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="67.5" spans="1:12">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3278,7 +3290,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3293,12 +3305,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3316,7 +3328,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3331,12 +3343,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" ht="69" spans="1:12">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3354,7 +3366,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3369,12 +3381,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" ht="54" spans="1:12">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3392,7 +3404,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3407,12 +3419,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3430,7 +3442,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3445,12 +3457,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="27" spans="1:12">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3468,7 +3480,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3480,15 +3492,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" ht="54" spans="1:12">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3506,13 +3518,13 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -3521,12 +3533,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="40.5" spans="1:12">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3544,7 +3556,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3556,15 +3568,15 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="42" spans="1:12">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3582,7 +3594,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3594,15 +3606,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="40.5" spans="1:12">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3620,7 +3632,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3635,12 +3647,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" ht="27" spans="1:12">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" ht="45" spans="1:12">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3658,13 +3670,13 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
@@ -3673,12 +3685,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3696,7 +3708,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3708,15 +3720,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="69" spans="1:12">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3734,7 +3746,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3749,12 +3761,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" ht="40.5" spans="1:12">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3772,7 +3784,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3787,12 +3799,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" ht="54" spans="1:12">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3810,7 +3822,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3825,12 +3837,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="40.5" spans="1:12">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3848,7 +3860,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3863,12 +3875,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" ht="55.5" spans="1:12">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3886,7 +3898,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3901,12 +3913,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" ht="69" spans="1:12">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3924,7 +3936,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3939,12 +3951,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" ht="54" spans="1:12">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3962,7 +3974,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3977,12 +3989,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4000,7 +4012,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4012,15 +4024,15 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L35" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" ht="40.5" spans="1:12">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4038,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4050,15 +4062,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L36" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" ht="43.5" spans="1:12">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4076,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4091,12 +4103,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" ht="54" spans="1:12">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4114,7 +4126,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4129,12 +4141,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" ht="54" spans="1:12">
       <c r="A39" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4152,7 +4164,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4164,15 +4176,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4190,7 +4202,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4205,12 +4217,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" ht="54" spans="1:12">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4228,7 +4240,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4243,12 +4255,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" ht="67.5" spans="1:12">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4266,7 +4278,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4281,12 +4293,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4304,7 +4316,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4319,12 +4331,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" ht="40.5" spans="1:12">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4342,7 +4354,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4357,12 +4369,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" ht="54" spans="1:12">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4380,7 +4392,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4395,12 +4407,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" ht="42" spans="1:12">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4418,7 +4430,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4433,12 +4445,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" ht="67.5" spans="1:12">
       <c r="A47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4456,7 +4468,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4471,12 +4483,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" ht="54" spans="1:12">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4494,7 +4506,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4509,12 +4521,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" ht="54" spans="1:12">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4532,7 +4544,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4547,12 +4559,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4570,7 +4582,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4582,15 +4594,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="L50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" ht="27" spans="1:12">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4608,7 +4620,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4623,15 +4635,15 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -4646,13 +4658,13 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
@@ -4661,12 +4673,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" ht="54" spans="1:12">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4684,10 +4696,10 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
@@ -4699,12 +4711,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" ht="54" spans="1:12">
       <c r="A54" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4722,27 +4734,27 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
       </c>
       <c r="I54" t="s">
-        <v>15</v>
+        <v>188</v>
       </c>
       <c r="J54" t="s">
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L54" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" ht="54" spans="1:12">
       <c r="A55" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4760,7 +4772,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4775,12 +4787,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" ht="27" spans="1:12">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4798,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4813,12 +4825,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4836,7 +4848,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4848,24 +4860,24 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L57" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B58" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4874,7 +4886,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4886,25 +4898,25 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L58" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" ht="55.5" spans="1:12">
       <c r="A59" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s">
         <v>203</v>
       </c>
-      <c r="B59" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" t="s">
-        <v>199</v>
-      </c>
       <c r="E59" t="s">
         <v>15</v>
       </c>
@@ -4912,7 +4924,7 @@
         <v>15</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4924,15 +4936,15 @@
         <v>15</v>
       </c>
       <c r="K59" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="L59" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4950,7 +4962,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4965,15 +4977,15 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -4988,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5003,12 +5015,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" ht="54" spans="1:12">
       <c r="A62" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5026,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5041,12 +5053,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5064,7 +5076,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5079,12 +5091,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5117,21 +5129,21 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" ht="42" spans="1:12">
       <c r="A65" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B65" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5140,7 +5152,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5152,15 +5164,15 @@
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L65" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" ht="30" spans="1:12">
       <c r="A66" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5169,7 +5181,7 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5178,7 +5190,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5190,15 +5202,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="L66" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" ht="28.5" spans="1:12">
       <c r="A67" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5216,7 +5228,7 @@
         <v>15</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5228,24 +5240,24 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L67" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="68" ht="210" spans="1:12">
       <c r="A68" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B68" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5254,7 +5266,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5266,15 +5278,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L68" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" ht="42" spans="1:12">
       <c r="A69" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5283,7 +5295,7 @@
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5292,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5304,15 +5316,15 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="L69" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" ht="54" spans="1:12">
       <c r="A70" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5330,7 +5342,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5345,21 +5357,21 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" ht="27" spans="1:12">
       <c r="A71" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B71" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5368,7 +5380,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5380,15 +5392,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="L71" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="72" ht="54" spans="1:12">
       <c r="A72" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5397,7 +5409,7 @@
         <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -5406,7 +5418,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5418,15 +5430,15 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="L72" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5444,7 +5456,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5459,12 +5471,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" ht="54" spans="1:12">
       <c r="A74" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5482,7 +5494,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5494,15 +5506,15 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L74" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" ht="54" spans="1:12">
       <c r="A75" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5520,7 +5532,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5535,12 +5547,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76" ht="28.5" spans="1:12">
       <c r="A76" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5558,7 +5570,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5573,12 +5585,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="77" ht="54" spans="1:12">
       <c r="A77" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5596,7 +5608,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5611,12 +5623,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="78" ht="40.5" spans="1:12">
       <c r="A78" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5634,7 +5646,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5649,12 +5661,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="79" ht="27" spans="1:12">
       <c r="A79" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5672,7 +5684,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5687,12 +5699,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" ht="27" spans="1:12">
       <c r="A80" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5710,7 +5722,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5725,12 +5737,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5748,7 +5760,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5763,12 +5775,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" ht="67.5" spans="1:12">
       <c r="A82" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5786,7 +5798,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5798,10 +5810,10 @@
         <v>15</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L82" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -5822,55 +5834,55 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5878,66 +5890,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B11" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B12" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B13" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B14" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B15" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -5959,616 +5971,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C6" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E6" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F6" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B7" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C7" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D7" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E7" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F7" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B8" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C8" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D8" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E8" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F8" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B9" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C9" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D9" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E9" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F9" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B10" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C10" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D10" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E10" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F10" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B11" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D11" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E11" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F11" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B12" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D12" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E12" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F12" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B13" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D13" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E13" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F13" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B14" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C14" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E14" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F14" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B15" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D15" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E15" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F15" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B16" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C16" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D16" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E16" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F16" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B17" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C17" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D17" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E17" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F17" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C18" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D18" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E18" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F18" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B19" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C19" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D19" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E19" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F19" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B20" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C20" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D20" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E20" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F20" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B21" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C21" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D21" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E21" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F21" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B22" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C22" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D22" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E22" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F22" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B23" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C23" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D23" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E23" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F23" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B24" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C24" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D24" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E24" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F24" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B25" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C25" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D25" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E25" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F25" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B26" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C26" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D26" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E26" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F26" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B27" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C27" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D27" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E27" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F27" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B28" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C28" t="s">
+        <v>443</v>
+      </c>
+      <c r="D28" t="s">
         <v>439</v>
       </c>
-      <c r="D28" t="s">
-        <v>435</v>
-      </c>
       <c r="E28" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F28" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B29" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C29" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D29" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E29" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F29" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B30" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C30" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D30" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E30" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="F30" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B31" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C31" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D31" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
